--- a/main/StructureDefinition-bc-facility-details-extension.xlsx
+++ b/main/StructureDefinition-bc-facility-details-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1268,7 +1268,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>111</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>117</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>122</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>123</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>128</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>129</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>134</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>135</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>140</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>145</v>
       </c>
@@ -3869,12 +3869,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK29">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
